--- a/Документы/МетодАнализаИерархий/1000minds-ahp-example-tables.xlsx
+++ b/Документы/МетодАнализаИерархий/1000minds-ahp-example-tables.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\src\repos\1000Minds WWW\src\Web\wwwroot\library\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DA76CCB-06CB-464F-9561-23BD27562982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="826" xr2:uid="{A6FABC54-0015-4255-A6F9-BC850A8E550B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="768" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="12" r:id="rId1"/>
@@ -26,7 +20,7 @@
     <sheet name="Tables 10a-10d" sheetId="10" r:id="rId11"/>
     <sheet name="Total scores" sheetId="11" r:id="rId12"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="145621"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -47,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="87">
   <si>
     <t>What is the Analytic Hierarchy Process (AHP)?</t>
   </si>
@@ -347,16 +341,85 @@
   <si>
     <t>https://www.1000minds.com/decision-making/analytic-hierarchy-process-ahp</t>
   </si>
+  <si>
+    <t>Таблица для выбора силовой установки</t>
+  </si>
+  <si>
+    <t>Вес</t>
+  </si>
+  <si>
+    <t>потребляемая 
+мощность в круизе</t>
+  </si>
+  <si>
+    <t>Тяга на взлете</t>
+  </si>
+  <si>
+    <t>легкость
+производство</t>
+  </si>
+  <si>
+    <t>веса</t>
+  </si>
+  <si>
+    <t>Легкость
+В производстве</t>
+  </si>
+  <si>
+    <t>тянущий</t>
+  </si>
+  <si>
+    <t>2тянущих</t>
+  </si>
+  <si>
+    <t>один толкающий</t>
+  </si>
+  <si>
+    <t>мощность</t>
+  </si>
+  <si>
+    <t>тяга на взлете</t>
+  </si>
+  <si>
+    <t>Итоговая таблица</t>
+  </si>
+  <si>
+    <t>толкающий</t>
+  </si>
+  <si>
+    <t>W производство</t>
+  </si>
+  <si>
+    <t>S производство</t>
+  </si>
+  <si>
+    <t>W вес</t>
+  </si>
+  <si>
+    <t>S вес</t>
+  </si>
+  <si>
+    <t>W мощность</t>
+  </si>
+  <si>
+    <t>S мощность</t>
+  </si>
+  <si>
+    <t>W тяга на взлете</t>
+  </si>
+  <si>
+    <t>S тяга на взлете</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -436,13 +499,24 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="18">
@@ -665,7 +739,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -784,10 +858,24 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -822,7 +910,7 @@
         <xdr:cNvPr id="6" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4DCE5198-5887-0ACF-C252-19085DAC521D}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4DCE5198-5887-0ACF-C252-19085DAC521D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -871,7 +959,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4FEAE78E-CEBD-467A-9AFB-BFAE17E0C522}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4FEAE78E-CEBD-467A-9AFB-BFAE17E0C522}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -946,7 +1034,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -998,7 +1086,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1192,14 +1280,14 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35191653-B809-4D88-B8E9-D99C66B3EE0F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B6:C29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1325,9 +1413,9 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B9" r:id="rId1" xr:uid="{43CCB1FC-F8D6-487E-B8DE-D84290FEA343}"/>
-    <hyperlink ref="B27" r:id="rId2" xr:uid="{E310BB0B-EBF0-48E5-AC5C-29A1CACAE09B}"/>
-    <hyperlink ref="B28" r:id="rId3" display="https://www.1000minds.com" xr:uid="{6D2B6F29-359B-47BB-9A95-8A930DC20928}"/>
+    <hyperlink ref="B9" r:id="rId1"/>
+    <hyperlink ref="B27" r:id="rId2"/>
+    <hyperlink ref="B28" r:id="rId3" display="https://www.1000minds.com"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId4"/>
@@ -1335,7 +1423,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6BC9A98-BEFE-4F0D-B578-E156B1996AE7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D35"/>
   <sheetFormatPr defaultColWidth="12.88671875" defaultRowHeight="14.85" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1670,7 +1758,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFAD3EA3-3E78-4422-BEEF-53EACC189DD2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K63"/>
   <sheetFormatPr defaultColWidth="12.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2667,7 +2755,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BFC91E2-29DB-40D3-B3D7-7745CA63386D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2842,8 +2930,8 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A13" r:id="rId1" xr:uid="{B375ECAF-9DB7-432D-8990-9892A0F2D1A3}"/>
-    <hyperlink ref="A12" r:id="rId2" xr:uid="{1DEFDC2E-45C1-49AD-875B-C8921D8D8DD4}"/>
+    <hyperlink ref="A13" r:id="rId1"/>
+    <hyperlink ref="A12" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId3"/>
@@ -2851,22 +2939,32 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D04A90D0-B647-4374-93B9-423542284CA2}">
-  <dimension ref="A1:J28"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:M68"/>
   <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="12.5546875" style="1"/>
+    <col min="1" max="1" width="17.5546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.5546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.44140625" style="1" customWidth="1"/>
+    <col min="6" max="7" width="12.5546875" style="1"/>
+    <col min="8" max="8" width="18.77734375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="16.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5546875" style="1"/>
+    <col min="11" max="11" width="21" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="12.5546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="47" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2"/>
     </row>
-    <row r="3" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
       <c r="B3" s="2" t="s">
         <v>8</v>
@@ -2886,7 +2984,7 @@
       <c r="I3"/>
       <c r="J3"/>
     </row>
-    <row r="4" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
@@ -2900,7 +2998,7 @@
       <c r="I4"/>
       <c r="J4"/>
     </row>
-    <row r="5" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -2914,7 +3012,7 @@
       <c r="I5"/>
       <c r="J5"/>
     </row>
-    <row r="6" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -2928,7 +3026,7 @@
       <c r="I6"/>
       <c r="J6"/>
     </row>
-    <row r="7" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>11</v>
       </c>
@@ -2942,7 +3040,7 @@
       <c r="I7"/>
       <c r="J7"/>
     </row>
-    <row r="8" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -2954,7 +3052,7 @@
       <c r="I8"/>
       <c r="J8"/>
     </row>
-    <row r="9" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9"/>
       <c r="B9"/>
       <c r="C9"/>
@@ -2966,18 +3064,21 @@
       <c r="I9"/>
       <c r="J9"/>
     </row>
-    <row r="10" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B10"/>
-      <c r="C10"/>
-      <c r="D10"/>
-      <c r="E10"/>
+    <row r="10" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A10" s="57" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" s="57"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
       <c r="F10"/>
       <c r="G10"/>
       <c r="H10"/>
       <c r="I10"/>
       <c r="J10"/>
     </row>
-    <row r="11" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B11"/>
       <c r="C11"/>
       <c r="D11"/>
@@ -2988,66 +3089,208 @@
       <c r="I11"/>
       <c r="J11"/>
     </row>
-    <row r="12" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B12"/>
-      <c r="C12"/>
-      <c r="D12"/>
-      <c r="E12"/>
-      <c r="F12"/>
-      <c r="G12"/>
-      <c r="H12"/>
-      <c r="I12"/>
-      <c r="J12"/>
-    </row>
-    <row r="13" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A13"/>
-      <c r="B13"/>
-      <c r="C13"/>
-      <c r="D13"/>
-      <c r="E13"/>
-      <c r="F13"/>
-      <c r="G13"/>
-      <c r="H13"/>
-      <c r="I13"/>
-      <c r="J13"/>
-    </row>
-    <row r="14" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A14"/>
-      <c r="B14"/>
-      <c r="C14"/>
-      <c r="D14"/>
-      <c r="E14"/>
-      <c r="F14"/>
-      <c r="G14"/>
-      <c r="H14"/>
-      <c r="I14"/>
-      <c r="J14"/>
-    </row>
-    <row r="15" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A15"/>
-      <c r="B15"/>
-      <c r="C15"/>
-      <c r="D15"/>
-      <c r="E15"/>
-      <c r="F15"/>
-      <c r="G15"/>
-      <c r="H15"/>
-      <c r="I15"/>
-      <c r="J15"/>
-    </row>
-    <row r="16" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A16"/>
-      <c r="B16"/>
-      <c r="C16"/>
-      <c r="D16"/>
-      <c r="E16"/>
-      <c r="F16"/>
-      <c r="G16"/>
-      <c r="H16"/>
-      <c r="I16"/>
-      <c r="J16"/>
-    </row>
-    <row r="17" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="50"/>
+      <c r="B12" s="52" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" s="51" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" s="52" t="s">
+        <v>67</v>
+      </c>
+      <c r="E12" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="F12" s="53"/>
+      <c r="G12" s="51"/>
+      <c r="H12" s="52" t="s">
+        <v>69</v>
+      </c>
+      <c r="I12" s="51" t="s">
+        <v>66</v>
+      </c>
+      <c r="J12" s="52" t="s">
+        <v>67</v>
+      </c>
+      <c r="K12" s="50" t="s">
+        <v>68</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="52" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" s="51">
+        <v>1</v>
+      </c>
+      <c r="C13" s="51">
+        <v>1</v>
+      </c>
+      <c r="D13" s="51">
+        <v>3</v>
+      </c>
+      <c r="E13" s="51">
+        <v>2</v>
+      </c>
+      <c r="F13" s="53"/>
+      <c r="G13" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="H13" s="51">
+        <v>4</v>
+      </c>
+      <c r="I13" s="51">
+        <v>16</v>
+      </c>
+      <c r="J13" s="51">
+        <v>7.5</v>
+      </c>
+      <c r="K13" s="51">
+        <v>10.25</v>
+      </c>
+      <c r="L13" s="1">
+        <f>SUM(H13:K13)</f>
+        <v>37.75</v>
+      </c>
+      <c r="M13" s="1">
+        <f>L13/$L$17</f>
+        <v>0.3775</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A14" s="51" t="s">
+        <v>66</v>
+      </c>
+      <c r="B14" s="51">
+        <v>1</v>
+      </c>
+      <c r="C14" s="51">
+        <v>1</v>
+      </c>
+      <c r="D14" s="51">
+        <f>1/C15</f>
+        <v>0.5</v>
+      </c>
+      <c r="E14" s="51">
+        <f>1/C16</f>
+        <v>0.25</v>
+      </c>
+      <c r="F14" s="53"/>
+      <c r="G14" s="51" t="s">
+        <v>66</v>
+      </c>
+      <c r="H14" s="51">
+        <v>2.2916666666666665</v>
+      </c>
+      <c r="I14" s="51">
+        <v>4</v>
+      </c>
+      <c r="J14" s="51">
+        <v>4.125</v>
+      </c>
+      <c r="K14" s="51">
+        <v>3.5</v>
+      </c>
+      <c r="L14" s="1">
+        <f t="shared" ref="L14:L16" si="0">SUM(H14:K14)</f>
+        <v>13.916666666666666</v>
+      </c>
+      <c r="M14" s="1">
+        <f t="shared" ref="M14:M16" si="1">L14/$L$17</f>
+        <v>0.13916666666666666</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="52" t="s">
+        <v>67</v>
+      </c>
+      <c r="B15" s="51">
+        <f>1/3</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C15" s="51">
+        <v>2</v>
+      </c>
+      <c r="D15" s="51">
+        <v>1</v>
+      </c>
+      <c r="E15" s="51">
+        <v>2</v>
+      </c>
+      <c r="F15" s="53"/>
+      <c r="G15" s="51" t="s">
+        <v>67</v>
+      </c>
+      <c r="H15" s="51">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="I15" s="51">
+        <v>12.333333333333334</v>
+      </c>
+      <c r="J15" s="51">
+        <v>4</v>
+      </c>
+      <c r="K15" s="51">
+        <v>5.1666666666666661</v>
+      </c>
+      <c r="L15" s="1">
+        <f t="shared" si="0"/>
+        <v>25.166666666666664</v>
+      </c>
+      <c r="M15" s="1">
+        <f t="shared" si="1"/>
+        <v>0.25166666666666665</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A16" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16" s="51">
+        <f>1/E13</f>
+        <v>0.5</v>
+      </c>
+      <c r="C16" s="51">
+        <v>4</v>
+      </c>
+      <c r="D16" s="51">
+        <f>1/E15</f>
+        <v>0.5</v>
+      </c>
+      <c r="E16" s="51">
+        <v>1</v>
+      </c>
+      <c r="F16" s="53"/>
+      <c r="G16" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="H16" s="51">
+        <v>5.166666666666667</v>
+      </c>
+      <c r="I16" s="51">
+        <v>9.5</v>
+      </c>
+      <c r="J16" s="51">
+        <v>4.5</v>
+      </c>
+      <c r="K16" s="51">
+        <v>4</v>
+      </c>
+      <c r="L16" s="1">
+        <f t="shared" si="0"/>
+        <v>23.166666666666668</v>
+      </c>
+      <c r="M16" s="1">
+        <f t="shared" si="1"/>
+        <v>0.23166666666666669</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17"/>
       <c r="B17"/>
       <c r="C17"/>
@@ -3058,8 +3301,12 @@
       <c r="H17"/>
       <c r="I17"/>
       <c r="J17"/>
-    </row>
-    <row r="18" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="L17" s="1">
+        <f>SUM(L13:L16)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18"/>
       <c r="B18"/>
       <c r="C18"/>
@@ -3071,7 +3318,7 @@
       <c r="I18"/>
       <c r="J18"/>
     </row>
-    <row r="19" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19"/>
       <c r="B19"/>
       <c r="C19"/>
@@ -3082,8 +3329,11 @@
       <c r="H19"/>
       <c r="I19"/>
       <c r="J19"/>
-    </row>
-    <row r="20" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="K19"/>
+      <c r="L19"/>
+      <c r="M19"/>
+    </row>
+    <row r="20" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A20"/>
       <c r="B20"/>
       <c r="C20"/>
@@ -3095,55 +3345,88 @@
       <c r="I20"/>
       <c r="J20"/>
     </row>
-    <row r="21" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A21"/>
       <c r="B21"/>
       <c r="C21"/>
       <c r="D21"/>
       <c r="E21"/>
       <c r="F21"/>
-      <c r="G21"/>
-      <c r="H21"/>
-      <c r="I21"/>
-      <c r="J21"/>
-    </row>
-    <row r="22" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="G21">
+        <f t="array" ref="G21:J24">MMULT(H13:K16,H13:K16)</f>
+        <v>133.125</v>
+      </c>
+      <c r="H21">
+        <v>317.875</v>
+      </c>
+      <c r="I21">
+        <v>172.125</v>
+      </c>
+      <c r="J21">
+        <v>176.75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A22"/>
       <c r="B22"/>
       <c r="C22"/>
       <c r="D22"/>
       <c r="E22"/>
       <c r="F22"/>
-      <c r="G22"/>
-      <c r="H22"/>
-      <c r="I22"/>
-      <c r="J22"/>
-    </row>
-    <row r="23" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="G22">
+        <v>51.541666666666671</v>
+      </c>
+      <c r="H22">
+        <v>136.79166666666666</v>
+      </c>
+      <c r="I22">
+        <v>65.9375</v>
+      </c>
+      <c r="J22">
+        <v>72.802083333333329</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A23"/>
       <c r="B23"/>
       <c r="C23"/>
       <c r="D23"/>
       <c r="E23"/>
       <c r="F23"/>
-      <c r="G23"/>
-      <c r="H23"/>
-      <c r="I23"/>
-      <c r="J23"/>
-    </row>
-    <row r="24" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="G23">
+        <v>84.291666666666671</v>
+      </c>
+      <c r="H23">
+        <v>206.41666666666669</v>
+      </c>
+      <c r="I23">
+        <v>117.625</v>
+      </c>
+      <c r="J23">
+        <v>122.08333333333331</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A24"/>
       <c r="B24"/>
       <c r="C24"/>
       <c r="D24"/>
       <c r="E24"/>
       <c r="F24"/>
-      <c r="G24"/>
-      <c r="H24"/>
-      <c r="I24"/>
-      <c r="J24"/>
-    </row>
-    <row r="25" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="G24">
+        <v>79.604166666666671</v>
+      </c>
+      <c r="H24">
+        <v>214.16666666666669</v>
+      </c>
+      <c r="I24">
+        <v>113.9375</v>
+      </c>
+      <c r="J24">
+        <v>125.45833333333334</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A25"/>
       <c r="B25"/>
       <c r="C25"/>
@@ -3155,7 +3438,7 @@
       <c r="I25"/>
       <c r="J25"/>
     </row>
-    <row r="26" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A26"/>
       <c r="B26"/>
       <c r="C26"/>
@@ -3167,7 +3450,7 @@
       <c r="I26"/>
       <c r="J26"/>
     </row>
-    <row r="27" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A27"/>
       <c r="B27"/>
       <c r="C27"/>
@@ -3179,26 +3462,756 @@
       <c r="I27"/>
       <c r="J27"/>
     </row>
-    <row r="28" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A28"/>
-      <c r="B28"/>
-      <c r="C28"/>
-      <c r="D28"/>
-      <c r="E28"/>
-      <c r="F28"/>
-      <c r="G28"/>
+    <row r="28" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A28" s="51"/>
+      <c r="B28" s="52" t="s">
+        <v>69</v>
+      </c>
+      <c r="C28" s="51" t="s">
+        <v>66</v>
+      </c>
+      <c r="D28" s="52" t="s">
+        <v>67</v>
+      </c>
+      <c r="E28" s="50" t="s">
+        <v>68</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="H28"/>
       <c r="I28"/>
       <c r="J28"/>
     </row>
+    <row r="29" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A29" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="B29" s="51">
+        <v>133.125</v>
+      </c>
+      <c r="C29" s="51">
+        <v>317.875</v>
+      </c>
+      <c r="D29" s="51">
+        <v>172.125</v>
+      </c>
+      <c r="E29" s="51">
+        <v>176.75</v>
+      </c>
+      <c r="F29" s="1">
+        <f>SUM(B29:E29)</f>
+        <v>799.875</v>
+      </c>
+      <c r="G29" s="1">
+        <f>F29/$F$33</f>
+        <v>0.36515114769533646</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A30" s="51" t="s">
+        <v>66</v>
+      </c>
+      <c r="B30" s="51">
+        <v>51.541666666666671</v>
+      </c>
+      <c r="C30" s="51">
+        <v>136.79166666666666</v>
+      </c>
+      <c r="D30" s="51">
+        <v>65.9375</v>
+      </c>
+      <c r="E30" s="51">
+        <v>72.802083333333329</v>
+      </c>
+      <c r="F30" s="1">
+        <f t="shared" ref="F30:F32" si="2">SUM(B30:E30)</f>
+        <v>327.07291666666663</v>
+      </c>
+      <c r="G30" s="1">
+        <f t="shared" ref="G30:G32" si="3">F30/$F$33</f>
+        <v>0.14931214364856316</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A31" s="51" t="s">
+        <v>67</v>
+      </c>
+      <c r="B31" s="51">
+        <v>84.291666666666671</v>
+      </c>
+      <c r="C31" s="51">
+        <v>206.41666666666669</v>
+      </c>
+      <c r="D31" s="51">
+        <v>117.625</v>
+      </c>
+      <c r="E31" s="51">
+        <v>122.08333333333331</v>
+      </c>
+      <c r="F31" s="1">
+        <f t="shared" si="2"/>
+        <v>530.41666666666674</v>
+      </c>
+      <c r="G31" s="1">
+        <f t="shared" si="3"/>
+        <v>0.24214065271457175</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A32" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="B32" s="51">
+        <v>79.604166666666671</v>
+      </c>
+      <c r="C32" s="51">
+        <v>214.16666666666669</v>
+      </c>
+      <c r="D32" s="51">
+        <v>113.9375</v>
+      </c>
+      <c r="E32" s="51">
+        <v>125.45833333333334</v>
+      </c>
+      <c r="F32" s="1">
+        <f t="shared" si="2"/>
+        <v>533.16666666666674</v>
+      </c>
+      <c r="G32" s="1">
+        <f t="shared" si="3"/>
+        <v>0.24339605594152869</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="F33" s="1">
+        <f>SUM(F29:F32)</f>
+        <v>2190.53125</v>
+      </c>
+      <c r="G33" s="1">
+        <f>SUM(G29:G32)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A38" s="54" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="50"/>
+      <c r="B39" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="C39" s="50" t="s">
+        <v>73</v>
+      </c>
+      <c r="D39" s="50" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="B40" s="50">
+        <v>1</v>
+      </c>
+      <c r="C40" s="50">
+        <v>3</v>
+      </c>
+      <c r="D40" s="50">
+        <v>4</v>
+      </c>
+      <c r="F40" s="1">
+        <f t="array" ref="F40:H42">MMULT(B40:D42,B40:D42)</f>
+        <v>3</v>
+      </c>
+      <c r="G40" s="1">
+        <v>14</v>
+      </c>
+      <c r="H40" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="I40" s="1">
+        <f>SUM(F40:H40)</f>
+        <v>26.5</v>
+      </c>
+      <c r="J40" s="1">
+        <f>I40/$I$43</f>
+        <v>0.63791374122367106</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="50" t="s">
+        <v>73</v>
+      </c>
+      <c r="B41" s="50">
+        <f>1/C40</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C41" s="50">
+        <v>1</v>
+      </c>
+      <c r="D41" s="50">
+        <f>1/C42</f>
+        <v>0.5</v>
+      </c>
+      <c r="F41" s="1">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="G41" s="1">
+        <v>3</v>
+      </c>
+      <c r="H41" s="1">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="I41" s="1">
+        <f t="shared" ref="I41:I42" si="4">SUM(F41:H41)</f>
+        <v>6.125</v>
+      </c>
+      <c r="J41" s="1">
+        <f t="shared" ref="J41:J42" si="5">I41/$I$43</f>
+        <v>0.14744232698094284</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="50" t="s">
+        <v>74</v>
+      </c>
+      <c r="B42" s="50">
+        <f>1/D40</f>
+        <v>0.25</v>
+      </c>
+      <c r="C42" s="50">
+        <v>2</v>
+      </c>
+      <c r="D42" s="50">
+        <v>1</v>
+      </c>
+      <c r="F42" s="1">
+        <v>1.1666666666666665</v>
+      </c>
+      <c r="G42" s="1">
+        <v>4.75</v>
+      </c>
+      <c r="H42" s="1">
+        <v>3</v>
+      </c>
+      <c r="I42" s="1">
+        <f t="shared" si="4"/>
+        <v>8.9166666666666661</v>
+      </c>
+      <c r="J42" s="1">
+        <f t="shared" si="5"/>
+        <v>0.21464393179538616</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I43" s="1">
+        <f>SUM(I40:I42)</f>
+        <v>41.541666666666664</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="54" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="50"/>
+      <c r="B45" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="C45" s="50" t="s">
+        <v>73</v>
+      </c>
+      <c r="D45" s="50" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="B46" s="50">
+        <v>1</v>
+      </c>
+      <c r="C46" s="50">
+        <v>2</v>
+      </c>
+      <c r="D46" s="50">
+        <v>1</v>
+      </c>
+      <c r="F46" s="1">
+        <f t="array" ref="F46:H48">MMULT(B46:D48,B46:D48)</f>
+        <v>3</v>
+      </c>
+      <c r="G46" s="1">
+        <v>6</v>
+      </c>
+      <c r="H46" s="1">
+        <v>3</v>
+      </c>
+      <c r="I46" s="1">
+        <f>SUM(F46:H46)</f>
+        <v>12</v>
+      </c>
+      <c r="J46" s="1">
+        <f>I46/$I$49</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" s="50" t="s">
+        <v>73</v>
+      </c>
+      <c r="B47" s="50">
+        <f>1/C46</f>
+        <v>0.5</v>
+      </c>
+      <c r="C47" s="50">
+        <v>1</v>
+      </c>
+      <c r="D47" s="50">
+        <f>1/C48</f>
+        <v>0.5</v>
+      </c>
+      <c r="F47" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="G47" s="1">
+        <v>3</v>
+      </c>
+      <c r="H47" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="I47" s="1">
+        <f t="shared" ref="I47:I48" si="6">SUM(F47:H47)</f>
+        <v>6</v>
+      </c>
+      <c r="J47" s="1">
+        <f t="shared" ref="J47:J48" si="7">I47/$I$49</f>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="50" t="s">
+        <v>74</v>
+      </c>
+      <c r="B48" s="50">
+        <f>1/D46</f>
+        <v>1</v>
+      </c>
+      <c r="C48" s="50">
+        <v>2</v>
+      </c>
+      <c r="D48" s="50">
+        <v>1</v>
+      </c>
+      <c r="F48" s="1">
+        <v>3</v>
+      </c>
+      <c r="G48" s="1">
+        <v>6</v>
+      </c>
+      <c r="H48" s="1">
+        <v>3</v>
+      </c>
+      <c r="I48" s="1">
+        <f t="shared" si="6"/>
+        <v>12</v>
+      </c>
+      <c r="J48" s="1">
+        <f t="shared" si="7"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I49" s="1">
+        <f>SUM(I46:I48)</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" s="54" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" s="50"/>
+      <c r="B51" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="C51" s="50" t="s">
+        <v>73</v>
+      </c>
+      <c r="D51" s="50" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="B52" s="50">
+        <v>1</v>
+      </c>
+      <c r="C52" s="50">
+        <v>2</v>
+      </c>
+      <c r="D52" s="50">
+        <v>1</v>
+      </c>
+      <c r="F52" s="1">
+        <f t="array" ref="F52:H54">MMULT(B52:D54,B52:D54)</f>
+        <v>3</v>
+      </c>
+      <c r="G52" s="1">
+        <v>6</v>
+      </c>
+      <c r="H52" s="1">
+        <v>3</v>
+      </c>
+      <c r="I52" s="1">
+        <f>SUM(F52:H52)</f>
+        <v>12</v>
+      </c>
+      <c r="J52" s="1">
+        <f>I52/$I$55</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" s="50" t="s">
+        <v>73</v>
+      </c>
+      <c r="B53" s="50">
+        <f>1/C52</f>
+        <v>0.5</v>
+      </c>
+      <c r="C53" s="50">
+        <v>1</v>
+      </c>
+      <c r="D53" s="50">
+        <f>1/C54</f>
+        <v>0.5</v>
+      </c>
+      <c r="F53" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="G53" s="1">
+        <v>3</v>
+      </c>
+      <c r="H53" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="I53" s="1">
+        <f t="shared" ref="I53:I54" si="8">SUM(F53:H53)</f>
+        <v>6</v>
+      </c>
+      <c r="J53" s="1">
+        <f t="shared" ref="J53:J54" si="9">I53/$I$55</f>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" s="50" t="s">
+        <v>74</v>
+      </c>
+      <c r="B54" s="50">
+        <f>1/D52</f>
+        <v>1</v>
+      </c>
+      <c r="C54" s="50">
+        <v>2</v>
+      </c>
+      <c r="D54" s="50">
+        <v>1</v>
+      </c>
+      <c r="F54" s="1">
+        <v>3</v>
+      </c>
+      <c r="G54" s="1">
+        <v>6</v>
+      </c>
+      <c r="H54" s="1">
+        <v>3</v>
+      </c>
+      <c r="I54" s="1">
+        <f t="shared" si="8"/>
+        <v>12</v>
+      </c>
+      <c r="J54" s="1">
+        <f t="shared" si="9"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I55" s="1">
+        <f>SUM(I52:I54)</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" s="54" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" s="50"/>
+      <c r="B57" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="C57" s="50" t="s">
+        <v>73</v>
+      </c>
+      <c r="D57" s="50" t="s">
+        <v>74</v>
+      </c>
+      <c r="F57" s="1">
+        <f t="array" ref="F57:H59">MMULT(B58:D60,B58:D60)</f>
+        <v>3</v>
+      </c>
+      <c r="G57" s="1">
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="H57" s="1">
+        <v>5</v>
+      </c>
+      <c r="I57" s="1">
+        <f>SUM(F57:H57)</f>
+        <v>9.3333333333333321</v>
+      </c>
+      <c r="J57" s="1">
+        <f>I57/$I$60</f>
+        <v>0.24778761061946902</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="B58" s="50">
+        <v>1</v>
+      </c>
+      <c r="C58" s="50">
+        <f>1/B59</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D58" s="50">
+        <v>2</v>
+      </c>
+      <c r="F58" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="G58" s="1">
+        <v>3</v>
+      </c>
+      <c r="H58" s="1">
+        <v>12</v>
+      </c>
+      <c r="I58" s="1">
+        <f t="shared" ref="I58:I59" si="10">SUM(F58:H58)</f>
+        <v>22.5</v>
+      </c>
+      <c r="J58" s="1">
+        <f t="shared" ref="J58:J59" si="11">I58/$I$60</f>
+        <v>0.59734513274336287</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" s="50" t="s">
+        <v>73</v>
+      </c>
+      <c r="B59" s="50">
+        <v>3</v>
+      </c>
+      <c r="C59" s="50">
+        <v>1</v>
+      </c>
+      <c r="D59" s="50">
+        <v>3</v>
+      </c>
+      <c r="F59" s="1">
+        <v>2</v>
+      </c>
+      <c r="G59" s="1">
+        <v>0.83333333333333326</v>
+      </c>
+      <c r="H59" s="1">
+        <v>3</v>
+      </c>
+      <c r="I59" s="1">
+        <f t="shared" si="10"/>
+        <v>5.833333333333333</v>
+      </c>
+      <c r="J59" s="1">
+        <f t="shared" si="11"/>
+        <v>0.15486725663716813</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" s="50" t="s">
+        <v>74</v>
+      </c>
+      <c r="B60" s="50">
+        <v>0.5</v>
+      </c>
+      <c r="C60" s="50">
+        <f>1/D59</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D60" s="50">
+        <v>1</v>
+      </c>
+      <c r="I60" s="1">
+        <f>SUM(I57:I59)</f>
+        <v>37.666666666666664</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A65" s="50"/>
+      <c r="B65" s="50" t="s">
+        <v>79</v>
+      </c>
+      <c r="C65" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="D65" s="50" t="s">
+        <v>81</v>
+      </c>
+      <c r="E65" s="50" t="s">
+        <v>82</v>
+      </c>
+      <c r="F65" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="G65" s="50" t="s">
+        <v>84</v>
+      </c>
+      <c r="H65" s="50" t="s">
+        <v>85</v>
+      </c>
+      <c r="I65" s="50" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A66" s="55" t="s">
+        <v>72</v>
+      </c>
+      <c r="B66" s="55">
+        <v>0.36515114769533646</v>
+      </c>
+      <c r="C66" s="55">
+        <v>0.63791374122367106</v>
+      </c>
+      <c r="D66" s="55">
+        <v>0.14931214364856316</v>
+      </c>
+      <c r="E66" s="55">
+        <v>0.4</v>
+      </c>
+      <c r="F66" s="55">
+        <v>0.24214065271457175</v>
+      </c>
+      <c r="G66" s="55">
+        <v>0.4</v>
+      </c>
+      <c r="H66" s="55">
+        <v>0.24339605594152869</v>
+      </c>
+      <c r="I66" s="55">
+        <v>0.2968369829683698</v>
+      </c>
+      <c r="J66" s="56">
+        <f>B66*C66+D66*E66+F66*G66+H66*I66</f>
+        <v>0.46176500419578725</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A67" s="50" t="s">
+        <v>73</v>
+      </c>
+      <c r="B67" s="50">
+        <v>0.36515114769533646</v>
+      </c>
+      <c r="C67" s="50">
+        <v>0.14744232698094284</v>
+      </c>
+      <c r="D67" s="50">
+        <v>0.14931214364856316</v>
+      </c>
+      <c r="E67" s="50">
+        <v>0.2</v>
+      </c>
+      <c r="F67" s="50">
+        <v>0.24214065271457175</v>
+      </c>
+      <c r="G67" s="50">
+        <v>0.2</v>
+      </c>
+      <c r="H67" s="50">
+        <v>0.24339605594152869</v>
+      </c>
+      <c r="I67" s="50">
+        <v>0.54014598540145986</v>
+      </c>
+      <c r="J67" s="1">
+        <f t="shared" ref="J67:J68" si="12">B67*C67+D67*E67+F67*G67+H67*I67</f>
+        <v>0.26359869666795521</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A68" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="B68" s="50">
+        <v>0.36515114769533646</v>
+      </c>
+      <c r="C68" s="50">
+        <v>0.21464393179538616</v>
+      </c>
+      <c r="D68" s="50">
+        <v>0.14931214364856316</v>
+      </c>
+      <c r="E68" s="50">
+        <v>0.4</v>
+      </c>
+      <c r="F68" s="50">
+        <v>0.24214065271457175</v>
+      </c>
+      <c r="G68" s="50">
+        <v>0.4</v>
+      </c>
+      <c r="H68" s="50">
+        <v>0.24339605594152869</v>
+      </c>
+      <c r="I68" s="50">
+        <v>0.16301703163017031</v>
+      </c>
+      <c r="J68" s="1">
+        <f t="shared" si="12"/>
+        <v>0.27463629913625764</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A10:E10"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{799DA2CF-BEDD-4BB8-A242-7FBE789FA360}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G17"/>
   <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3389,7 +4402,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EC69034-EBFC-4603-8837-41901C2D1A87}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H12"/>
   <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -3497,7 +4510,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EA14424-AE7E-467E-B4CC-5AC08134F54A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M18"/>
   <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -3804,7 +4817,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F3DE911-617B-4A0B-8D3B-6883D05546F1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F7"/>
   <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -3921,7 +4934,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65C820FC-B9AA-4DD7-8323-5038A2AB9463}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -4074,7 +5087,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8060A9DD-D202-4C26-85C3-8A93F02D11C0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L18"/>
   <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4424,7 +5437,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF36CDE1-7F9E-477F-A964-C78E2445DD08}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D6"/>
   <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
